--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244996</v>
+        <v>121244971</v>
       </c>
       <c r="B2" t="n">
-        <v>74517</v>
+        <v>91312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506722</v>
+        <v>506793</v>
       </c>
       <c r="R2" t="n">
-        <v>6320925</v>
+        <v>6320856</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244971</v>
+        <v>121244996</v>
       </c>
       <c r="B3" t="n">
-        <v>91302</v>
+        <v>74520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506793</v>
+        <v>506722</v>
       </c>
       <c r="R3" t="n">
-        <v>6320856</v>
+        <v>6320925</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244971</v>
+        <v>121244996</v>
       </c>
       <c r="B2" t="n">
-        <v>91312</v>
+        <v>74520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506793</v>
+        <v>506722</v>
       </c>
       <c r="R2" t="n">
-        <v>6320856</v>
+        <v>6320925</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244996</v>
+        <v>121244971</v>
       </c>
       <c r="B3" t="n">
-        <v>74520</v>
+        <v>91312</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506722</v>
+        <v>506793</v>
       </c>
       <c r="R3" t="n">
-        <v>6320925</v>
+        <v>6320856</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121244996</v>
       </c>
       <c r="B2" t="n">
-        <v>74520</v>
+        <v>74522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121244971</v>
       </c>
       <c r="B3" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244996</v>
+        <v>121244971</v>
       </c>
       <c r="B2" t="n">
-        <v>74522</v>
+        <v>91325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506722</v>
+        <v>506793</v>
       </c>
       <c r="R2" t="n">
-        <v>6320925</v>
+        <v>6320856</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244971</v>
+        <v>121244996</v>
       </c>
       <c r="B3" t="n">
-        <v>91324</v>
+        <v>74522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506793</v>
+        <v>506722</v>
       </c>
       <c r="R3" t="n">
-        <v>6320856</v>
+        <v>6320925</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244971</v>
+        <v>121244996</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>74525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506793</v>
+        <v>506722</v>
       </c>
       <c r="R2" t="n">
-        <v>6320856</v>
+        <v>6320925</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244996</v>
+        <v>121244971</v>
       </c>
       <c r="B3" t="n">
-        <v>74522</v>
+        <v>91328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506722</v>
+        <v>506793</v>
       </c>
       <c r="R3" t="n">
-        <v>6320925</v>
+        <v>6320856</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121244996</v>
       </c>
       <c r="B2" t="n">
-        <v>74525</v>
+        <v>74526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121244971</v>
       </c>
       <c r="B3" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121244996</v>
       </c>
       <c r="B2" t="n">
-        <v>74526</v>
+        <v>74527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121244971</v>
       </c>
       <c r="B3" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36774-2023 artfynd.xlsx
+++ b/artfynd/A 36774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244996</v>
+        <v>121244971</v>
       </c>
       <c r="B2" t="n">
-        <v>74527</v>
+        <v>91335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506722</v>
+        <v>506793</v>
       </c>
       <c r="R2" t="n">
-        <v>6320925</v>
+        <v>6320856</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244971</v>
+        <v>121244996</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
+        <v>74527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506793</v>
+        <v>506722</v>
       </c>
       <c r="R3" t="n">
-        <v>6320856</v>
+        <v>6320925</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
